--- a/Output/Tables/tab_regressions.xlsx
+++ b/Output/Tables/tab_regressions.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="107">
   <si>
     <t>Husband-Self-reported</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Wife-DNA</t>
   </si>
   <si>
-    <t>Joint Coop</t>
+    <t>Coop Member</t>
   </si>
   <si>
     <t>Household Credit</t>
@@ -37,22 +37,16 @@
     <t>Extension Access</t>
   </si>
   <si>
-    <t>Cellphone</t>
-  </si>
-  <si>
-    <t>Fertilizer</t>
-  </si>
-  <si>
-    <t>Consumption (%)</t>
-  </si>
-  <si>
-    <t>Zone 1</t>
-  </si>
-  <si>
-    <t>Zone 3</t>
-  </si>
-  <si>
-    <t>Zone 4</t>
+    <t>Consump perc</t>
+  </si>
+  <si>
+    <t>Zone1</t>
+  </si>
+  <si>
+    <t>Zone3</t>
+  </si>
+  <si>
+    <t>Zone4</t>
   </si>
   <si>
     <t>Age</t>
@@ -73,295 +67,256 @@
     <t>N</t>
   </si>
   <si>
-    <t>0.115*</t>
+    <t>0.199***</t>
+  </si>
+  <si>
+    <t>(0.032)</t>
+  </si>
+  <si>
+    <t>-0.056</t>
+  </si>
+  <si>
+    <t>(0.067)</t>
+  </si>
+  <si>
+    <t>0.417***</t>
   </si>
   <si>
     <t>(0.062)</t>
   </si>
   <si>
-    <t>-0.049</t>
-  </si>
-  <si>
-    <t>(0.066)</t>
-  </si>
-  <si>
-    <t>0.427***</t>
-  </si>
-  <si>
-    <t>0.268</t>
-  </si>
-  <si>
-    <t>(0.427)</t>
-  </si>
-  <si>
-    <t>0.091***</t>
+    <t>-0.002</t>
+  </si>
+  <si>
+    <t>(0.004)</t>
+  </si>
+  <si>
+    <t>-0.099***</t>
   </si>
   <si>
     <t>(0.022)</t>
   </si>
   <si>
-    <t>-0.002</t>
-  </si>
-  <si>
-    <t>(0.004)</t>
-  </si>
-  <si>
-    <t>-0.138***</t>
-  </si>
-  <si>
-    <t>(0.029)</t>
-  </si>
-  <si>
-    <t>-0.703***</t>
-  </si>
-  <si>
-    <t>(0.050)</t>
-  </si>
-  <si>
-    <t>0.297***</t>
-  </si>
-  <si>
-    <t>(0.069)</t>
+    <t>-0.637***</t>
+  </si>
+  <si>
+    <t>(0.028)</t>
+  </si>
+  <si>
+    <t>0.339***</t>
+  </si>
+  <si>
+    <t>(0.068)</t>
+  </si>
+  <si>
+    <t>0.003</t>
+  </si>
+  <si>
+    <t>(0.005)</t>
+  </si>
+  <si>
+    <t>-0.010*</t>
+  </si>
+  <si>
+    <t>0.069***</t>
+  </si>
+  <si>
+    <t>(0.014)</t>
+  </si>
+  <si>
+    <t>-0.143</t>
+  </si>
+  <si>
+    <t>(0.251)</t>
+  </si>
+  <si>
+    <t>-0.052</t>
+  </si>
+  <si>
+    <t>(0.147)</t>
+  </si>
+  <si>
+    <t>729</t>
+  </si>
+  <si>
+    <t>-0.099</t>
+  </si>
+  <si>
+    <t>(0.085)</t>
+  </si>
+  <si>
+    <t>-0.015</t>
+  </si>
+  <si>
+    <t>(0.122)</t>
+  </si>
+  <si>
+    <t>0.244***</t>
+  </si>
+  <si>
+    <t>(0.094)</t>
+  </si>
+  <si>
+    <t>-0.001</t>
+  </si>
+  <si>
+    <t>(0.007)</t>
+  </si>
+  <si>
+    <t>0.182***</t>
+  </si>
+  <si>
+    <t>(0.039)</t>
+  </si>
+  <si>
+    <t>-0.622***</t>
+  </si>
+  <si>
+    <t>(0.098)</t>
+  </si>
+  <si>
+    <t>0.313***</t>
+  </si>
+  <si>
+    <t>(0.102)</t>
+  </si>
+  <si>
+    <t>(0.009)</t>
+  </si>
+  <si>
+    <t>0.008</t>
+  </si>
+  <si>
+    <t>(0.021)</t>
+  </si>
+  <si>
+    <t>0.050**</t>
+  </si>
+  <si>
+    <t>-0.083</t>
+  </si>
+  <si>
+    <t>(0.300)</t>
+  </si>
+  <si>
+    <t>-0.158</t>
+  </si>
+  <si>
+    <t>(0.407)</t>
+  </si>
+  <si>
+    <t>0.018</t>
+  </si>
+  <si>
+    <t>(0.088)</t>
+  </si>
+  <si>
+    <t>-0.003</t>
+  </si>
+  <si>
+    <t>(0.100)</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>(0.116)</t>
+  </si>
+  <si>
+    <t>-0.004***</t>
+  </si>
+  <si>
+    <t>(0.001)</t>
+  </si>
+  <si>
+    <t>-0.245***</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>-0.478***</t>
+  </si>
+  <si>
+    <t>(0.023)</t>
+  </si>
+  <si>
+    <t>0.344***</t>
+  </si>
+  <si>
+    <t>(0.061)</t>
+  </si>
+  <si>
+    <t>0.008***</t>
+  </si>
+  <si>
+    <t>(0.003)</t>
   </si>
   <si>
     <t>0.002</t>
   </si>
   <si>
-    <t>(0.005)</t>
-  </si>
-  <si>
-    <t>-0.010</t>
-  </si>
-  <si>
-    <t>(0.008)</t>
-  </si>
-  <si>
-    <t>0.068***</t>
-  </si>
-  <si>
-    <t>(0.018)</t>
-  </si>
-  <si>
-    <t>-0.143</t>
-  </si>
-  <si>
-    <t>(0.230)</t>
-  </si>
-  <si>
-    <t>-0.257</t>
-  </si>
-  <si>
-    <t>(0.384)</t>
-  </si>
-  <si>
-    <t>729</t>
-  </si>
-  <si>
-    <t>(0.162)</t>
-  </si>
-  <si>
-    <t>-0.033</t>
-  </si>
-  <si>
-    <t>(0.125)</t>
-  </si>
-  <si>
-    <t>0.210**</t>
-  </si>
-  <si>
-    <t>(0.096)</t>
-  </si>
-  <si>
-    <t>-0.086</t>
-  </si>
-  <si>
-    <t>(0.342)</t>
-  </si>
-  <si>
-    <t>0.247*</t>
-  </si>
-  <si>
-    <t>(0.146)</t>
-  </si>
-  <si>
-    <t>-0.001</t>
-  </si>
-  <si>
-    <t>0.186***</t>
+    <t>-0.004</t>
+  </si>
+  <si>
+    <t>(0.013)</t>
+  </si>
+  <si>
+    <t>0.292**</t>
+  </si>
+  <si>
+    <t>(0.143)</t>
+  </si>
+  <si>
+    <t>0.145</t>
+  </si>
+  <si>
+    <t>(0.352)</t>
+  </si>
+  <si>
+    <t>(0.057)</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>(0.141)</t>
+  </si>
+  <si>
+    <t>-0.106</t>
+  </si>
+  <si>
+    <t>(0.139)</t>
+  </si>
+  <si>
+    <t>(0.002)</t>
+  </si>
+  <si>
+    <t>-0.164***</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>-0.579***</t>
+  </si>
+  <si>
+    <t>(0.033)</t>
+  </si>
+  <si>
+    <t>0.321***</t>
   </si>
   <si>
     <t>(0.052)</t>
   </si>
   <si>
-    <t>-0.643***</t>
-  </si>
-  <si>
-    <t>(0.087)</t>
-  </si>
-  <si>
-    <t>0.318***</t>
-  </si>
-  <si>
-    <t>(0.117)</t>
-  </si>
-  <si>
-    <t>0.003</t>
-  </si>
-  <si>
-    <t>0.006</t>
-  </si>
-  <si>
-    <t>(0.019)</t>
-  </si>
-  <si>
-    <t>0.049**</t>
-  </si>
-  <si>
-    <t>(0.024)</t>
-  </si>
-  <si>
-    <t>-0.094</t>
-  </si>
-  <si>
-    <t>(0.290)</t>
-  </si>
-  <si>
-    <t>-0.132</t>
-  </si>
-  <si>
-    <t>(0.650)</t>
-  </si>
-  <si>
-    <t>0.091</t>
-  </si>
-  <si>
-    <t>(0.098)</t>
-  </si>
-  <si>
-    <t>-0.005</t>
-  </si>
-  <si>
-    <t>(0.106)</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>(0.109)</t>
-  </si>
-  <si>
-    <t>0.027</t>
-  </si>
-  <si>
-    <t>(0.213)</t>
-  </si>
-  <si>
-    <t>-0.128</t>
-  </si>
-  <si>
-    <t>(0.112)</t>
-  </si>
-  <si>
-    <t>-0.004***</t>
-  </si>
-  <si>
-    <t>(0.001)</t>
-  </si>
-  <si>
-    <t>-0.203***</t>
-  </si>
-  <si>
-    <t>(0.039)</t>
-  </si>
-  <si>
-    <t>-0.429***</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>0.377***</t>
-  </si>
-  <si>
-    <t>(0.046)</t>
-  </si>
-  <si>
-    <t>0.008***</t>
-  </si>
-  <si>
-    <t>(0.002)</t>
-  </si>
-  <si>
-    <t>-0.004</t>
-  </si>
-  <si>
-    <t>(0.012)</t>
-  </si>
-  <si>
-    <t>0.300**</t>
-  </si>
-  <si>
-    <t>(0.151)</t>
-  </si>
-  <si>
-    <t>0.114</t>
-  </si>
-  <si>
-    <t>(0.368)</t>
-  </si>
-  <si>
-    <t>-0.056</t>
-  </si>
-  <si>
-    <t>(0.065)</t>
-  </si>
-  <si>
-    <t>0.099</t>
-  </si>
-  <si>
-    <t>(0.143)</t>
-  </si>
-  <si>
-    <t>-0.122</t>
-  </si>
-  <si>
-    <t>(0.141)</t>
-  </si>
-  <si>
-    <t>-0.075</t>
-  </si>
-  <si>
-    <t>(0.457)</t>
-  </si>
-  <si>
-    <t>0.122</t>
-  </si>
-  <si>
-    <t>(0.172)</t>
-  </si>
-  <si>
-    <t>-0.165**</t>
-  </si>
-  <si>
-    <t>(0.073)</t>
-  </si>
-  <si>
-    <t>-0.593***</t>
-  </si>
-  <si>
-    <t>(0.070)</t>
-  </si>
-  <si>
-    <t>0.321***</t>
-  </si>
-  <si>
     <t>0.015***</t>
   </si>
   <si>
     <t>0.012</t>
   </si>
   <si>
-    <t>(0.016)</t>
+    <t>(0.017)</t>
   </si>
   <si>
     <t>-0.014</t>
@@ -370,16 +325,16 @@
     <t>(0.034)</t>
   </si>
   <si>
-    <t>-0.009</t>
-  </si>
-  <si>
-    <t>(0.319)</t>
-  </si>
-  <si>
-    <t>-0.183</t>
-  </si>
-  <si>
-    <t>(0.502)</t>
+    <t>-0.006</t>
+  </si>
+  <si>
+    <t>(0.316)</t>
+  </si>
+  <si>
+    <t>-0.219</t>
+  </si>
+  <si>
+    <t>(0.192)</t>
   </si>
 </sst>
 </file>
@@ -737,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -759,31 +714,31 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" t="s">
         <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -791,31 +746,31 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -823,31 +778,31 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1"/>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -855,31 +810,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>104</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1"/>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -887,31 +842,31 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1"/>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -919,31 +874,31 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1"/>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -951,31 +906,31 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1"/>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -983,31 +938,31 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1"/>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1015,31 +970,31 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1"/>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1047,31 +1002,31 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1"/>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1079,31 +1034,31 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1"/>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1111,31 +1066,31 @@
         <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E24" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1"/>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D25" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E25" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1143,80 +1098,16 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="E26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="1"/>
-      <c r="B27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E27" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" t="s">
-        <v>96</v>
-      </c>
-      <c r="E28" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="1"/>
-      <c r="B29" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29" t="s">
-        <v>97</v>
-      </c>
-      <c r="E29" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" t="s">
-        <v>46</v>
-      </c>
-      <c r="E30" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
